--- a/Results/PP Proportions/PP_Content_AO_Analysis.xlsx
+++ b/Results/PP Proportions/PP_Content_AO_Analysis.xlsx
@@ -1519,13 +1519,13 @@
         <v>111</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.2984</v>
+        <v>-0.0955</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.467</v>
+        <v>-0.1703</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1535</v>
+        <v>-0.0395</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1539,19 +1539,19 @@
         <v>112</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.306</v>
+        <v>-0.1038</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.5006</v>
+        <v>-0.1914</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1535</v>
+        <v>-0.0252</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.0018</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.9982</v>
       </c>
     </row>
     <row r="8">
@@ -1559,13 +1559,13 @@
         <v>113</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2876</v>
+        <v>0.0996</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1449</v>
+        <v>0.0408</v>
       </c>
       <c r="D8" t="n">
-        <v>0.448</v>
+        <v>0.1755</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -1579,19 +1579,19 @@
         <v>114</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0095</v>
+        <v>0.0043</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.034</v>
+        <v>-0.0119</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0084</v>
+        <v>0.0253</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1075</v>
+        <v>0.7125</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8925</v>
+        <v>0.2875</v>
       </c>
     </row>
     <row r="10">
@@ -1599,19 +1599,19 @@
         <v>115</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2758</v>
+        <v>0.1132</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1006</v>
+        <v>0.0228</v>
       </c>
       <c r="D10" t="n">
-        <v>0.452</v>
+        <v>0.2338</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0.9978</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="11">
@@ -1619,19 +1619,19 @@
         <v>116</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0175</v>
+        <v>-0.0039</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0535</v>
+        <v>-0.032</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0119</v>
+        <v>0.0272</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0798</v>
+        <v>0.3648</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9202</v>
+        <v>0.6352</v>
       </c>
     </row>
     <row r="12">
@@ -1639,19 +1639,19 @@
         <v>117</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0092</v>
+        <v>-0.0132</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.2439</v>
+        <v>-0.1506</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2471</v>
+        <v>0.118</v>
       </c>
       <c r="E12" t="n">
-        <v>0.53</v>
+        <v>0.4195</v>
       </c>
       <c r="F12" t="n">
-        <v>0.47</v>
+        <v>0.5805</v>
       </c>
     </row>
     <row r="13">
@@ -1659,19 +1659,19 @@
         <v>118</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.2867</v>
+        <v>-0.1084</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.4707</v>
+        <v>-0.233</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1235</v>
+        <v>-0.0192</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.0035</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.9965</v>
       </c>
     </row>
     <row r="14">
@@ -1679,13 +1679,13 @@
         <v>119</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.296</v>
+        <v>-0.1174</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.4631</v>
+        <v>-0.2206</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1368</v>
+        <v>-0.0446</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1699,19 +1699,19 @@
         <v>120</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0074</v>
+        <v>0.0087</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0144</v>
+        <v>-0.0257</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0355</v>
+        <v>0.041</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7898</v>
+        <v>0.727</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2102</v>
+        <v>0.273</v>
       </c>
     </row>
     <row r="16">
@@ -1719,19 +1719,19 @@
         <v>121</v>
       </c>
       <c r="B16" t="n">
-        <v>0.2873</v>
+        <v>0.0948</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1228</v>
+        <v>0.015</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4748</v>
+        <v>0.1869</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0.9942</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.0058</v>
       </c>
     </row>
     <row r="17">
@@ -1739,19 +1739,19 @@
         <v>122</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.0088</v>
+        <v>0.0005</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0525</v>
+        <v>-0.0433</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0272</v>
+        <v>0.0346</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2738</v>
+        <v>0.512</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7262</v>
+        <v>0.488</v>
       </c>
     </row>
     <row r="18">
@@ -1759,19 +1759,19 @@
         <v>123</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0004</v>
+        <v>-0.0041</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.044</v>
+        <v>-0.0444</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0456</v>
+        <v>0.0281</v>
       </c>
       <c r="E18" t="n">
-        <v>0.512</v>
+        <v>0.3895</v>
       </c>
       <c r="F18" t="n">
-        <v>0.488</v>
+        <v>0.6105</v>
       </c>
     </row>
     <row r="19">
@@ -1779,13 +1779,13 @@
         <v>124</v>
       </c>
       <c r="B19" t="n">
-        <v>0.278</v>
+        <v>0.1091</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1342</v>
+        <v>0.0387</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4337</v>
+        <v>0.203</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -1799,19 +1799,19 @@
         <v>125</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.0169</v>
+        <v>-0.0079</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0431</v>
+        <v>-0.0307</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0017</v>
+        <v>0.0085</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002</v>
+        <v>0.1255</v>
       </c>
       <c r="F20" t="n">
-        <v>0.998</v>
+        <v>0.8745</v>
       </c>
     </row>
   </sheetData>
@@ -1854,13 +1854,13 @@
         <v>49</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3169</v>
+        <v>0.1364</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2012</v>
+        <v>0.0746</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4507</v>
+        <v>0.2113</v>
       </c>
     </row>
     <row r="5">
@@ -1868,13 +1868,13 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0165</v>
+        <v>0.0269</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0077</v>
+        <v>0.013</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0317</v>
+        <v>0.0459</v>
       </c>
     </row>
     <row r="6">
@@ -1882,13 +1882,13 @@
         <v>51</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0312</v>
+        <v>0.029</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0134</v>
+        <v>0.0137</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0559</v>
+        <v>0.0496</v>
       </c>
     </row>
     <row r="7">
@@ -1926,13 +1926,13 @@
         <v>58</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2997</v>
+        <v>0.1085</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1914</v>
+        <v>0.0609</v>
       </c>
       <c r="D10" t="n">
-        <v>0.425</v>
+        <v>0.1768</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -1946,13 +1946,13 @@
         <v>59</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2847</v>
+        <v>0.1068</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1788</v>
+        <v>0.0532</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3994</v>
+        <v>0.1672</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -1966,19 +1966,19 @@
         <v>60</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0141</v>
+        <v>-0.0019</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0327</v>
+        <v>-0.0162</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0005</v>
+        <v>0.0118</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0122</v>
+        <v>0.3685</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9878</v>
+        <v>0.6315</v>
       </c>
     </row>
   </sheetData>
@@ -2021,13 +2021,13 @@
         <v>63</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1242</v>
+        <v>0.0613</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0592</v>
+        <v>0.0278</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2006</v>
+        <v>0.1018</v>
       </c>
     </row>
     <row r="5">
@@ -2035,13 +2035,13 @@
         <v>64</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1174</v>
+        <v>0.0643</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0528</v>
+        <v>0.0257</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1904</v>
+        <v>0.1208</v>
       </c>
     </row>
     <row r="6">
@@ -2079,19 +2079,19 @@
         <v>66</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0058</v>
+        <v>-0.0024</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0999</v>
+        <v>-0.0685</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1032</v>
+        <v>0.0597</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5532</v>
+        <v>0.466</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4468</v>
+        <v>0.534</v>
       </c>
     </row>
   </sheetData>
@@ -2140,13 +2140,13 @@
         <v>63</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3205</v>
+        <v>0.127</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1605</v>
+        <v>0.0595</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5061</v>
+        <v>0.2162</v>
       </c>
     </row>
     <row r="5">
@@ -2157,13 +2157,13 @@
         <v>64</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3087</v>
+        <v>0.1403</v>
       </c>
       <c r="D5" t="n">
-        <v>0.137</v>
+        <v>0.0516</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4823</v>
+        <v>0.2565</v>
       </c>
     </row>
     <row r="6">
@@ -2174,13 +2174,13 @@
         <v>63</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0197</v>
+        <v>0.0304</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006</v>
+        <v>0.0118</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0442</v>
+        <v>0.0575</v>
       </c>
     </row>
     <row r="7">
@@ -2191,13 +2191,13 @@
         <v>64</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0119</v>
+        <v>0.0218</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0032</v>
+        <v>0.0067</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0264</v>
+        <v>0.0459</v>
       </c>
     </row>
     <row r="8">
@@ -2208,13 +2208,13 @@
         <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03</v>
+        <v>0.0258</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0097</v>
+        <v>0.0109</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0649</v>
+        <v>0.0484</v>
       </c>
     </row>
     <row r="9">
@@ -2225,13 +2225,13 @@
         <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0294</v>
+        <v>0.0301</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0096</v>
+        <v>0.0098</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0669</v>
+        <v>0.0647</v>
       </c>
     </row>
     <row r="10">
@@ -2275,19 +2275,19 @@
         <v>49</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0092</v>
+        <v>-0.0132</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.2439</v>
+        <v>-0.1506</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2471</v>
+        <v>0.118</v>
       </c>
       <c r="F13" t="n">
-        <v>0.53</v>
+        <v>0.4195</v>
       </c>
       <c r="G13" t="n">
-        <v>0.47</v>
+        <v>0.5805</v>
       </c>
     </row>
     <row r="14">
@@ -2298,19 +2298,19 @@
         <v>50</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0074</v>
+        <v>0.0087</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0144</v>
+        <v>-0.0257</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0355</v>
+        <v>0.041</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7898</v>
+        <v>0.727</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2102</v>
+        <v>0.273</v>
       </c>
     </row>
     <row r="15">
@@ -2321,19 +2321,19 @@
         <v>51</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0004</v>
+        <v>-0.0041</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.044</v>
+        <v>-0.0444</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0456</v>
+        <v>0.0281</v>
       </c>
       <c r="F15" t="n">
-        <v>0.512</v>
+        <v>0.3895</v>
       </c>
       <c r="G15" t="n">
-        <v>0.488</v>
+        <v>0.6105</v>
       </c>
     </row>
     <row r="16">
@@ -2377,13 +2377,13 @@
         <v>63</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2984</v>
+        <v>0.0955</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1535</v>
+        <v>0.0395</v>
       </c>
       <c r="E19" t="n">
-        <v>0.467</v>
+        <v>0.1703</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -2400,13 +2400,13 @@
         <v>63</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2876</v>
+        <v>0.0996</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1449</v>
+        <v>0.0408</v>
       </c>
       <c r="E20" t="n">
-        <v>0.448</v>
+        <v>0.1755</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -2423,19 +2423,19 @@
         <v>63</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0095</v>
+        <v>0.0043</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.034</v>
+        <v>-0.0119</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0084</v>
+        <v>0.0253</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1075</v>
+        <v>0.7125</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8925</v>
+        <v>0.2875</v>
       </c>
     </row>
     <row r="22">
@@ -2446,13 +2446,13 @@
         <v>64</v>
       </c>
       <c r="C22" t="n">
-        <v>0.296</v>
+        <v>0.1174</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1368</v>
+        <v>0.0446</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4631</v>
+        <v>0.2206</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -2469,13 +2469,13 @@
         <v>64</v>
       </c>
       <c r="C23" t="n">
-        <v>0.278</v>
+        <v>0.1091</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1342</v>
+        <v>0.0387</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4337</v>
+        <v>0.203</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -2492,19 +2492,19 @@
         <v>64</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0169</v>
+        <v>-0.0079</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0431</v>
+        <v>-0.0307</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.0017</v>
+        <v>0.0085</v>
       </c>
       <c r="F24" t="n">
-        <v>0.002</v>
+        <v>0.1255</v>
       </c>
       <c r="G24" t="n">
-        <v>0.998</v>
+        <v>0.8745</v>
       </c>
     </row>
   </sheetData>
@@ -2558,19 +2558,19 @@
         <v>20</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0045</v>
+        <v>0.0034</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0055</v>
+        <v>-0.0022</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0132</v>
+        <v>0.0098</v>
       </c>
       <c r="E5" t="n">
-        <v>0.809</v>
+        <v>0.8778</v>
       </c>
       <c r="F5" t="n">
-        <v>0.191</v>
+        <v>0.1222</v>
       </c>
     </row>
     <row r="6">
@@ -2608,19 +2608,19 @@
         <v>49</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0107</v>
+        <v>0.008</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0137</v>
+        <v>-0.0047</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0337</v>
+        <v>0.0211</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7942</v>
+        <v>0.894</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2057</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="10">
@@ -2631,16 +2631,16 @@
         <v>0.0014</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0012</v>
+        <v>-0.0018</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0038</v>
+        <v>0.0049</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8988</v>
+        <v>0.8285</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1013</v>
+        <v>0.1715</v>
       </c>
     </row>
     <row r="11">
@@ -2648,19 +2648,19 @@
         <v>51</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0013</v>
+        <v>0.0007</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0038</v>
+        <v>-0.0029</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0052</v>
+        <v>0.0044</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7362</v>
+        <v>0.677</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2638</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="12">
@@ -2698,19 +2698,19 @@
         <v>58</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0092</v>
+        <v>0.0065</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0143</v>
+        <v>-0.0049</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0306</v>
+        <v>0.0173</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7745</v>
+        <v>0.8852</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2255</v>
+        <v>0.1148</v>
       </c>
     </row>
     <row r="16">
@@ -2718,19 +2718,19 @@
         <v>59</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0094</v>
+        <v>0.0072</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0132</v>
+        <v>-0.0037</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0294</v>
+        <v>0.018</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7915</v>
+        <v>0.9092</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2085</v>
+        <v>0.0907</v>
       </c>
     </row>
     <row r="17">
@@ -2738,19 +2738,19 @@
         <v>60</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0001</v>
+        <v>0.0007</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0032</v>
+        <v>-0.0023</v>
       </c>
       <c r="D17" t="n">
-        <v>0.004</v>
+        <v>0.0036</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5295</v>
+        <v>0.692</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4705</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="18">
@@ -2788,19 +2788,19 @@
         <v>63</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0034</v>
+        <v>0.0024</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0091</v>
+        <v>-0.0054</v>
       </c>
       <c r="D21" t="n">
-        <v>0.015</v>
+        <v>0.0105</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7175</v>
+        <v>0.7602</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2825</v>
+        <v>0.2397</v>
       </c>
     </row>
     <row r="22">
@@ -2808,19 +2808,19 @@
         <v>64</v>
       </c>
       <c r="B22" t="n">
-        <v>0.0059</v>
+        <v>0.0044</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0074</v>
+        <v>-0.0047</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0158</v>
+        <v>0.0128</v>
       </c>
       <c r="E22" t="n">
-        <v>0.827</v>
+        <v>0.8602</v>
       </c>
       <c r="F22" t="n">
-        <v>0.173</v>
+        <v>0.1398</v>
       </c>
     </row>
     <row r="23">
@@ -2858,19 +2858,19 @@
         <v>66</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.0025</v>
+        <v>-0.0019</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0165</v>
+        <v>-0.0114</v>
       </c>
       <c r="D26" t="n">
-        <v>0.012</v>
+        <v>0.0106</v>
       </c>
       <c r="E26" t="n">
-        <v>0.369</v>
+        <v>0.3698</v>
       </c>
       <c r="F26" t="n">
-        <v>0.631</v>
+        <v>0.6302</v>
       </c>
     </row>
   </sheetData>
@@ -2924,19 +2924,19 @@
         <v>24</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0064</v>
+        <v>0.0019</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0007</v>
+        <v>-0.0023</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0135</v>
+        <v>0.0058</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9812</v>
+        <v>0.835</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0187</v>
+        <v>0.165</v>
       </c>
     </row>
     <row r="6">
@@ -2974,19 +2974,19 @@
         <v>49</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0205</v>
+        <v>0.0072</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0063</v>
+        <v>-0.0012</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0382</v>
+        <v>0.016</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9948</v>
+        <v>0.9562</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0053</v>
+        <v>0.0437</v>
       </c>
     </row>
     <row r="10">
@@ -2994,19 +2994,19 @@
         <v>50</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0003</v>
+        <v>-0.0007</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0019</v>
+        <v>-0.0031</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001</v>
+        <v>0.0013</v>
       </c>
       <c r="E10" t="n">
-        <v>0.286</v>
+        <v>0.2293</v>
       </c>
       <c r="F10" t="n">
-        <v>0.714</v>
+        <v>0.7708</v>
       </c>
     </row>
     <row r="11">
@@ -3014,19 +3014,19 @@
         <v>51</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0007</v>
+        <v>-0.0008</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0039</v>
+        <v>-0.0037</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0019</v>
+        <v>0.0015</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2695</v>
+        <v>0.218</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7305</v>
+        <v>0.782</v>
       </c>
     </row>
     <row r="12">
@@ -3064,19 +3064,19 @@
         <v>58</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0209</v>
+        <v>0.0079</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0075</v>
+        <v>0.0009</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0377</v>
+        <v>0.0155</v>
       </c>
       <c r="E15" t="n">
-        <v>0.997</v>
+        <v>0.9835</v>
       </c>
       <c r="F15" t="n">
-        <v>0.003</v>
+        <v>0.0165</v>
       </c>
     </row>
     <row r="16">
@@ -3084,19 +3084,19 @@
         <v>59</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0214</v>
+        <v>0.0081</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0085</v>
+        <v>0.0011</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0369</v>
+        <v>0.0154</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9988</v>
+        <v>0.9902</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0013</v>
+        <v>0.0098</v>
       </c>
     </row>
     <row r="17">
@@ -3104,19 +3104,19 @@
         <v>60</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0004</v>
+        <v>0.0002</v>
       </c>
       <c r="C17" t="n">
         <v>-0.0014</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0027</v>
+        <v>0.0021</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6852</v>
+        <v>0.5808</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3147</v>
+        <v>0.4192</v>
       </c>
     </row>
     <row r="18">
@@ -3154,19 +3154,19 @@
         <v>63</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0026</v>
+        <v>-0.0008</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0033</v>
+        <v>-0.0052</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0095</v>
+        <v>0.0038</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8048</v>
+        <v>0.3505</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1952</v>
+        <v>0.6495</v>
       </c>
     </row>
     <row r="22">
@@ -3174,19 +3174,19 @@
         <v>64</v>
       </c>
       <c r="B22" t="n">
-        <v>0.0102</v>
+        <v>0.0046</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0002</v>
+        <v>-0.0023</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0206</v>
+        <v>0.0116</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9715</v>
+        <v>0.9158</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0285</v>
+        <v>0.0843</v>
       </c>
     </row>
     <row r="23">
@@ -3224,19 +3224,19 @@
         <v>66</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.0075</v>
+        <v>-0.0054</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0187</v>
+        <v>-0.013</v>
       </c>
       <c r="D26" t="n">
-        <v>0.004</v>
+        <v>0.0034</v>
       </c>
       <c r="E26" t="n">
-        <v>0.095</v>
+        <v>0.0948</v>
       </c>
       <c r="F26" t="n">
-        <v>0.905</v>
+        <v>0.9052</v>
       </c>
     </row>
   </sheetData>
@@ -3290,13 +3290,13 @@
         <v>25</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.04</v>
+        <v>-0.0203</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.047</v>
+        <v>-0.0284</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0314</v>
+        <v>-0.0135</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3340,13 +3340,13 @@
         <v>49</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.1155</v>
+        <v>-0.0618</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1336</v>
+        <v>-0.0847</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.092</v>
+        <v>-0.0402</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -3360,19 +3360,19 @@
         <v>50</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0013</v>
+        <v>0.0035</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0003</v>
+        <v>0.001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0033</v>
+        <v>0.0069</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9695</v>
+        <v>0.9998</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0305</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="11">
@@ -3380,19 +3380,19 @@
         <v>51</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.0055</v>
+        <v>-0.0029</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.011</v>
+        <v>-0.0056</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0018</v>
+        <v>-0.0008</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.0018</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0.9982</v>
       </c>
     </row>
     <row r="12">
@@ -3430,13 +3430,13 @@
         <v>58</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.1171</v>
+        <v>-0.0654</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1359</v>
+        <v>-0.0912</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.093</v>
+        <v>-0.0435</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3450,13 +3450,13 @@
         <v>59</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.1095</v>
+        <v>-0.0588</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.1262</v>
+        <v>-0.0822</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0874</v>
+        <v>-0.0398</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3470,13 +3470,13 @@
         <v>60</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0069</v>
+        <v>0.0065</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0026</v>
+        <v>0.0029</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0129</v>
+        <v>0.0112</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -3520,13 +3520,13 @@
         <v>63</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.0487</v>
+        <v>-0.0251</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0596</v>
+        <v>-0.0366</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0347</v>
+        <v>-0.0135</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -3540,13 +3540,13 @@
         <v>64</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.0322</v>
+        <v>-0.0154</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0391</v>
+        <v>-0.0238</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0231</v>
+        <v>-0.0079</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -3590,19 +3590,19 @@
         <v>66</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.0166</v>
+        <v>-0.0097</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0313</v>
+        <v>-0.0242</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.001</v>
+        <v>0.004</v>
       </c>
       <c r="E26" t="n">
-        <v>0.026</v>
+        <v>0.0875</v>
       </c>
       <c r="F26" t="n">
-        <v>0.974</v>
+        <v>0.9125</v>
       </c>
     </row>
   </sheetData>
@@ -3677,19 +3677,19 @@
         <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0107</v>
+        <v>0.0078</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0114</v>
+        <v>-0.0041</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0317</v>
+        <v>0.0199</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8182</v>
+        <v>0.912</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1818</v>
+        <v>0.088</v>
       </c>
     </row>
     <row r="9">
@@ -3700,19 +3700,19 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0013</v>
+        <v>0.0012</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0013</v>
+        <v>-0.002</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0034</v>
+        <v>0.0045</v>
       </c>
       <c r="F9" t="n">
-        <v>0.883</v>
+        <v>0.7855</v>
       </c>
       <c r="G9" t="n">
-        <v>0.117</v>
+        <v>0.2145</v>
       </c>
     </row>
     <row r="10">
@@ -3723,19 +3723,19 @@
         <v>96</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001</v>
+        <v>0.0004</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0038</v>
+        <v>-0.0031</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0048</v>
+        <v>0.0042</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6935</v>
+        <v>0.6048</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3065</v>
+        <v>0.3952</v>
       </c>
     </row>
     <row r="11">
@@ -3746,19 +3746,19 @@
         <v>97</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0105</v>
+        <v>0.0082</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0148</v>
+        <v>-0.006</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0368</v>
+        <v>0.0222</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7705</v>
+        <v>0.8772</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2295</v>
+        <v>0.1227</v>
       </c>
     </row>
     <row r="12">
@@ -3769,19 +3769,19 @@
         <v>97</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.001</v>
+        <v>-0.0015</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0041</v>
+        <v>0.0055</v>
       </c>
       <c r="F12" t="n">
-        <v>0.91</v>
+        <v>0.861</v>
       </c>
       <c r="G12" t="n">
-        <v>0.09</v>
+        <v>0.139</v>
       </c>
     </row>
     <row r="13">
@@ -3792,19 +3792,19 @@
         <v>97</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0016</v>
+        <v>0.001</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0034</v>
+        <v>-0.0025</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0059</v>
+        <v>0.0051</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7758</v>
+        <v>0.7345</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2242</v>
+        <v>0.2655</v>
       </c>
     </row>
     <row r="14">
@@ -3848,19 +3848,19 @@
         <v>99</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0002</v>
+        <v>0.0002</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0061</v>
+        <v>-0.0033</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0058</v>
+        <v>0.0043</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4752</v>
+        <v>0.549</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5248</v>
+        <v>0.451</v>
       </c>
     </row>
     <row r="18">
@@ -3871,19 +3871,19 @@
         <v>99</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0003</v>
+        <v>0.0005</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0002</v>
+        <v>-0.0003</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0009</v>
+        <v>0.0016</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9255</v>
+        <v>0.9185</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0745</v>
+        <v>0.0815</v>
       </c>
     </row>
     <row r="19">
@@ -3900,13 +3900,13 @@
         <v>-0.0002</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0017</v>
+        <v>0.0018</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9475</v>
+        <v>0.9485</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0525</v>
+        <v>0.0515</v>
       </c>
     </row>
   </sheetData>
@@ -3981,19 +3981,19 @@
         <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0117</v>
+        <v>0.0104</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0155</v>
+        <v>-0.0067</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0372</v>
+        <v>0.0272</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7867</v>
+        <v>0.8875</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2132</v>
+        <v>0.1125</v>
       </c>
     </row>
     <row r="9">
@@ -4007,16 +4007,16 @@
         <v>0.0014</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.001</v>
+        <v>-0.0015</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0037</v>
+        <v>0.0046</v>
       </c>
       <c r="F9" t="n">
-        <v>0.907</v>
+        <v>0.8418</v>
       </c>
       <c r="G9" t="n">
-        <v>0.093</v>
+        <v>0.1582</v>
       </c>
     </row>
     <row r="10">
@@ -4027,19 +4027,19 @@
         <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0013</v>
+        <v>0.0006</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0045</v>
+        <v>-0.0032</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0061</v>
+        <v>0.0049</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7102</v>
+        <v>0.64</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2898</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="11">
@@ -4050,19 +4050,19 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0088</v>
+        <v>0.0057</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0126</v>
+        <v>-0.0037</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0251</v>
+        <v>0.015</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8018</v>
+        <v>0.9065</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1983</v>
+        <v>0.0935</v>
       </c>
     </row>
     <row r="12">
@@ -4076,16 +4076,16 @@
         <v>0.0015</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0012</v>
+        <v>-0.0021</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004</v>
+        <v>0.0055</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8892</v>
+        <v>0.808</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1108</v>
+        <v>0.192</v>
       </c>
     </row>
     <row r="13">
@@ -4096,19 +4096,19 @@
         <v>106</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0012</v>
+        <v>0.0008</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0028</v>
+        <v>-0.0025</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0047</v>
+        <v>0.0043</v>
       </c>
       <c r="F13" t="n">
-        <v>0.761</v>
+        <v>0.708</v>
       </c>
       <c r="G13" t="n">
-        <v>0.239</v>
+        <v>0.292</v>
       </c>
     </row>
     <row r="14">
@@ -4152,19 +4152,19 @@
         <v>108</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0026</v>
+        <v>-0.0045</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0128</v>
+        <v>-0.0134</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0054</v>
+        <v>0.0034</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2732</v>
+        <v>0.142</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7268</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="18">
@@ -4178,16 +4178,16 @@
         <v>0.0001</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0005</v>
+        <v>-0.001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0006</v>
+        <v>0.0014</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6528</v>
+        <v>0.5938</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3472</v>
+        <v>0.4062</v>
       </c>
     </row>
     <row r="19">
@@ -4198,19 +4198,19 @@
         <v>108</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0001</v>
+        <v>0.0002</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0018</v>
+        <v>-0.0009</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0018</v>
+        <v>0.0012</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4312</v>
+        <v>0.6402</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5688</v>
+        <v>0.3598</v>
       </c>
     </row>
   </sheetData>
